--- a/data/trans_dic/P34B01_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,32; 51,74</t>
+          <t>40,99; 51,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,1; 57,12</t>
+          <t>46,95; 57,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,92; 70,72</t>
+          <t>62,0; 70,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,92; 54,24</t>
+          <t>41,67; 54,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,83; 63,43</t>
+          <t>52,58; 63,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,6; 69,36</t>
+          <t>61,92; 69,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,0; 50,7</t>
+          <t>42,89; 51,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,01; 58,18</t>
+          <t>50,93; 58,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,99; 68,81</t>
+          <t>63,16; 69,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 47,24</t>
+          <t>36,45; 46,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,92; 65,0</t>
+          <t>54,71; 64,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,07; 75,87</t>
+          <t>67,41; 76,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,74; 60,25</t>
+          <t>48,76; 60,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,27; 63,42</t>
+          <t>52,28; 62,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,79; 70,92</t>
+          <t>62,2; 70,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,29; 51,15</t>
+          <t>43,57; 51,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,09; 62,5</t>
+          <t>55,2; 62,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,24; 72,42</t>
+          <t>66,19; 72,16</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 48,12</t>
+          <t>39,89; 48,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,84; 59,25</t>
+          <t>51,27; 59,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 65,51</t>
+          <t>16,18; 65,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 49,46</t>
+          <t>36,77; 49,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,03; 62,91</t>
+          <t>46,28; 61,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,87; 64,99</t>
+          <t>52,89; 65,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,3; 47,23</t>
+          <t>40,27; 47,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,39; 58,93</t>
+          <t>51,06; 59,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 63,8</t>
+          <t>22,23; 63,54</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,19; 51,22</t>
+          <t>45,27; 50,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,05; 56,91</t>
+          <t>50,33; 56,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,21; 64,88</t>
+          <t>58,36; 65,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,43; 53,88</t>
+          <t>46,59; 54,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,01; 56,7</t>
+          <t>49,82; 57,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,93; 85,59</t>
+          <t>64,92; 86,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,62; 51,23</t>
+          <t>46,49; 51,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,69; 56,03</t>
+          <t>51,48; 56,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,8; 76,56</t>
+          <t>62,62; 78,44</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,49; 51,2</t>
+          <t>41,92; 51,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,29; 58,6</t>
+          <t>50,33; 58,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,38; 66,81</t>
+          <t>56,88; 66,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,05; 52,34</t>
+          <t>44,88; 52,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,25; 56,28</t>
+          <t>49,38; 56,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,0; 61,25</t>
+          <t>40,48; 61,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,02; 50,73</t>
+          <t>45,18; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,8; 56,38</t>
+          <t>50,71; 56,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,21; 62,03</t>
+          <t>46,39; 61,77</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,0; 32,24</t>
+          <t>21,62; 32,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,2; 53,48</t>
+          <t>41,34; 53,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,56; 72,37</t>
+          <t>50,51; 72,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,76; 52,9</t>
+          <t>46,81; 52,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,14; 53,5</t>
+          <t>47,26; 53,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,56; 56,11</t>
+          <t>49,64; 56,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,64; 48,02</t>
+          <t>42,55; 47,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,11; 52,69</t>
+          <t>47,22; 52,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,52; 58,6</t>
+          <t>51,45; 58,7</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,84; 46,37</t>
+          <t>42,75; 46,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,43; 55,94</t>
+          <t>52,3; 55,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47,4; 64,8</t>
+          <t>46,25; 64,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,7; 51,11</t>
+          <t>47,72; 51,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,75; 55,13</t>
+          <t>51,44; 55,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,36; 69,05</t>
+          <t>58,07; 67,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,74; 48,17</t>
+          <t>45,8; 48,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,45; 54,97</t>
+          <t>52,4; 54,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,38; 64,61</t>
+          <t>54,48; 64,49</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>180639; 226222</t>
+          <t>179234; 222991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>202096; 245100</t>
+          <t>201449; 246631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312820; 357290</t>
+          <t>313232; 357169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131831; 170551</t>
+          <t>131019; 169911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>183358; 220140</t>
+          <t>182484; 220421</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>274385; 308935</t>
+          <t>275819; 309533</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>323235; 381109</t>
+          <t>322373; 384152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>395949; 451556</t>
+          <t>395254; 451767</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>598835; 654101</t>
+          <t>600408; 657628</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155125; 197849</t>
+          <t>152651; 194219</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>207158; 245215</t>
+          <t>206367; 243340</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303294; 343080</t>
+          <t>304856; 345226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164735; 203638</t>
+          <t>164802; 203198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>198315; 236090</t>
+          <t>194638; 234153</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>239295; 270275</t>
+          <t>237039; 269402</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>327651; 387073</t>
+          <t>329749; 387497</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>412927; 468467</t>
+          <t>413700; 468397</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>552013; 603502</t>
+          <t>551563; 601375</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>250645; 302421</t>
+          <t>250722; 303796</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>265352; 309238</t>
+          <t>267586; 312748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106482; 436896</t>
+          <t>107909; 440083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97600; 128652</t>
+          <t>95655; 128248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76462; 104502</t>
+          <t>76881; 102946</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87598; 107677</t>
+          <t>87631; 108414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>358089; 419719</t>
+          <t>357885; 419269</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>353570; 405450</t>
+          <t>351324; 406534</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>156630; 531246</t>
+          <t>185126; 529011</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>523700; 593590</t>
+          <t>524739; 589590</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>586903; 654311</t>
+          <t>578595; 653559</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>599870; 668559</t>
+          <t>601431; 672095</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>355094; 412064</t>
+          <t>356288; 413732</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>412980; 468234</t>
+          <t>411458; 471387</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>633348; 834788</t>
+          <t>633230; 844884</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>896865; 985583</t>
+          <t>894317; 987880</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1021076; 1106889</t>
+          <t>1016923; 1110094</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1259724; 1535716</t>
+          <t>1256106; 1573365</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>216957; 261415</t>
+          <t>214057; 260953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>312129; 363745</t>
+          <t>312379; 361989</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>270411; 314859</t>
+          <t>268057; 313469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>343087; 398562</t>
+          <t>341768; 400648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>363566; 415495</t>
+          <t>364537; 416510</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>317764; 512211</t>
+          <t>338530; 513013</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>572663; 645375</t>
+          <t>574724; 645286</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>690336; 766172</t>
+          <t>689077; 766178</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>604200; 811078</t>
+          <t>606622; 807721</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58446; 85658</t>
+          <t>57450; 86897</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>118313; 153553</t>
+          <t>118708; 153755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116941; 170763</t>
+          <t>119191; 171280</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>518701; 586822</t>
+          <t>519301; 583916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>510069; 578867</t>
+          <t>511401; 576659</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>374015; 423483</t>
+          <t>374667; 426338</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>586263; 660331</t>
+          <t>585022; 659757</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>645051; 721454</t>
+          <t>646569; 719109</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>510398; 580489</t>
+          <t>509703; 581473</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2004004</t>
+          <t>2004005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1465038; 1585846</t>
+          <t>1462087; 1583935</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1775289; 1894131</t>
+          <t>1770823; 1895670</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1593718; 2178784</t>
+          <t>1554929; 2179337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1692659; 1813377</t>
+          <t>1693319; 1816345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1827705; 1946826</t>
+          <t>1816728; 1948976</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2076664; 2457222</t>
+          <t>2066623; 2415047</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3187081; 3356802</t>
+          <t>3191114; 3363684</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3627834; 3802215</t>
+          <t>3624523; 3799951</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3624990; 4471175</t>
+          <t>3770684; 4463031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B01_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,99; 51,0</t>
+          <t>41,56; 51,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,95; 57,48</t>
+          <t>47,13; 56,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,0; 70,7</t>
+          <t>63,37; 71,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,67; 54,03</t>
+          <t>41,72; 52,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,58; 63,51</t>
+          <t>52,13; 62,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,92; 69,49</t>
+          <t>62,36; 69,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,89; 51,11</t>
+          <t>43,12; 51,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,93; 58,21</t>
+          <t>50,56; 58,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63,16; 69,18</t>
+          <t>64,17; 69,91</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,45; 46,38</t>
+          <t>36,37; 46,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,71; 64,51</t>
+          <t>54,62; 64,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,41; 76,34</t>
+          <t>67,6; 75,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,76; 60,12</t>
+          <t>48,46; 60,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,28; 62,9</t>
+          <t>52,92; 63,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,2; 70,69</t>
+          <t>62,02; 69,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,57; 51,2</t>
+          <t>43,65; 51,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,2; 62,49</t>
+          <t>54,91; 62,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,19; 72,16</t>
+          <t>66,19; 72,03</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,89; 48,34</t>
+          <t>40,13; 48,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,27; 59,92</t>
+          <t>50,86; 59,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 65,98</t>
+          <t>60,81; 69,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,77; 49,3</t>
+          <t>36,82; 49,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,28; 61,97</t>
+          <t>46,27; 62,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,89; 65,44</t>
+          <t>52,33; 65,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,27; 47,18</t>
+          <t>40,27; 47,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,06; 59,09</t>
+          <t>51,16; 58,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,23; 63,54</t>
+          <t>59,7; 67,12</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,27; 50,87</t>
+          <t>44,97; 51,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,33; 56,85</t>
+          <t>51,2; 56,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,36; 65,22</t>
+          <t>59,69; 66,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,59; 54,1</t>
+          <t>46,61; 54,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,82; 57,08</t>
+          <t>50,11; 57,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,92; 86,62</t>
+          <t>63,97; 69,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 51,35</t>
+          <t>46,56; 51,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,48; 56,19</t>
+          <t>51,65; 55,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,62; 78,44</t>
+          <t>62,38; 66,86</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,92; 51,11</t>
+          <t>42,12; 50,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,33; 58,32</t>
+          <t>51,02; 58,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,88; 66,52</t>
+          <t>56,22; 65,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,88; 52,61</t>
+          <t>44,89; 52,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,38; 56,42</t>
+          <t>48,98; 56,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,48; 61,35</t>
+          <t>59,79; 65,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,18; 50,73</t>
+          <t>45,14; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,71; 56,38</t>
+          <t>51,08; 56,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,39; 61,77</t>
+          <t>59,52; 64,58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 32,7</t>
+          <t>22,23; 33,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,34; 53,55</t>
+          <t>41,11; 53,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50,51; 72,59</t>
+          <t>56,47; 75,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,81; 52,64</t>
+          <t>46,5; 52,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,26; 53,29</t>
+          <t>47,14; 53,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,64; 56,49</t>
+          <t>49,71; 56,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,55; 47,98</t>
+          <t>42,53; 48,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,22; 52,52</t>
+          <t>46,9; 52,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,45; 58,7</t>
+          <t>52,55; 59,32</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,75; 46,32</t>
+          <t>42,63; 46,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,3; 55,99</t>
+          <t>52,47; 55,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,25; 64,82</t>
+          <t>63,62; 67,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,72; 51,19</t>
+          <t>47,67; 51,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,44; 55,19</t>
+          <t>51,67; 55,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,07; 67,87</t>
+          <t>60,72; 63,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,8; 48,27</t>
+          <t>45,83; 48,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,4; 54,93</t>
+          <t>52,44; 54,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54,48; 64,49</t>
+          <t>62,54; 64,82</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>335703</t>
+          <t>373388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>292335</t>
+          <t>321415</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>628039</t>
+          <t>694804</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>179234; 222991</t>
+          <t>181702; 225806</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201449; 246631</t>
+          <t>202221; 242928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313232; 357169</t>
+          <t>348908; 395117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131019; 169911</t>
+          <t>131183; 166108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182484; 220421</t>
+          <t>180920; 218139</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>275819; 309533</t>
+          <t>303282; 340092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>322373; 384152</t>
+          <t>324137; 384164</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>395254; 451767</t>
+          <t>392394; 451428</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>600408; 657628</t>
+          <t>665367; 724922</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324789</t>
+          <t>347266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>253944</t>
+          <t>279758</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>578732</t>
+          <t>627023</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>152651; 194219</t>
+          <t>152306; 195097</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206367; 243340</t>
+          <t>206037; 244472</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>304856; 345226</t>
+          <t>326673; 366444</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164802; 203198</t>
+          <t>163800; 204666</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194638; 234153</t>
+          <t>197006; 236740</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>237039; 269402</t>
+          <t>261518; 295008</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>329749; 387497</t>
+          <t>330310; 389629</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>413700; 468397</t>
+          <t>411565; 466871</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>551563; 601375</t>
+          <t>598946; 651771</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270569</t>
+          <t>307018</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98096</t>
+          <t>109333</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>368665</t>
+          <t>416351</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>250722; 303796</t>
+          <t>252228; 301872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>267586; 312748</t>
+          <t>265465; 308986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107909; 440083</t>
+          <t>285988; 329138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95655; 128248</t>
+          <t>95782; 128159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76881; 102946</t>
+          <t>76862; 103347</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87631; 108414</t>
+          <t>97435; 121252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>357885; 419269</t>
+          <t>357888; 421947</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>351324; 406534</t>
+          <t>352013; 404768</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185126; 529011</t>
+          <t>391938; 440612</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635567</t>
+          <t>713088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>712705</t>
+          <t>571697</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1348271</t>
+          <t>1284785</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>524739; 589590</t>
+          <t>521253; 594114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>578595; 653559</t>
+          <t>588587; 652965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>601431; 672095</t>
+          <t>671941; 749466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>356288; 413732</t>
+          <t>356488; 414529</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>411458; 471387</t>
+          <t>413810; 473550</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>633230; 844884</t>
+          <t>549121; 598077</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>894317; 987880</t>
+          <t>895684; 985857</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1016923; 1110094</t>
+          <t>1020385; 1104929</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1256106; 1573365</t>
+          <t>1237756; 1326571</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291209</t>
+          <t>345095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>453029</t>
+          <t>518315</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>744238</t>
+          <t>863409</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>214057; 260953</t>
+          <t>215086; 260191</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>312379; 361989</t>
+          <t>316655; 363260</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>268057; 313469</t>
+          <t>317037; 368856</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>341768; 400648</t>
+          <t>341820; 398194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>364537; 416510</t>
+          <t>361566; 416216</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>338530; 513013</t>
+          <t>494555; 541110</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>574724; 645286</t>
+          <t>574288; 645357</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>689077; 766178</t>
+          <t>694095; 767358</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>606622; 807721</t>
+          <t>827972; 898296</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146168</t>
+          <t>154415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>399166</t>
+          <t>445668</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>545333</t>
+          <t>600082</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57450; 86897</t>
+          <t>59078; 88204</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>118708; 153755</t>
+          <t>118031; 152469</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119191; 171280</t>
+          <t>131128; 175511</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>519301; 583916</t>
+          <t>515852; 587068</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>511401; 576659</t>
+          <t>510077; 578882</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>374667; 426338</t>
+          <t>416334; 474800</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>585022; 659757</t>
+          <t>584868; 660368</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>646569; 719109</t>
+          <t>642208; 722586</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>509703; 581473</t>
+          <t>562117; 634510</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2004005</t>
+          <t>2240270</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2209274</t>
+          <t>2246186</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4213279</t>
+          <t>4486456</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1462087; 1583935</t>
+          <t>1457795; 1581789</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1770823; 1895670</t>
+          <t>1776655; 1887412</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1554929; 2179337</t>
+          <t>2179808; 2301724</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1693319; 1816345</t>
+          <t>1691368; 1818102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1816728; 1948976</t>
+          <t>1824801; 1950066</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2066623; 2415047</t>
+          <t>2196315; 2295142</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3191114; 3363684</t>
+          <t>3193710; 3359698</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3624523; 3799951</t>
+          <t>3627124; 3792438</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3770684; 4463031</t>
+          <t>4404578; 4565201</t>
         </is>
       </c>
     </row>
